--- a/data/trans_orig/P21-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>220522</t>
+          <t>220876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>242667</t>
+          <t>243995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190246</t>
+          <t>189679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217095</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>419666</t>
+          <t>421461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>454563</t>
+          <t>456117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -846,97 +846,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52488</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70592</t>
+          <t>71159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79285</t>
+          <t>77731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114182</t>
+          <t>112387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397647</t>
+          <t>398096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433011</t>
+          <t>431138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356037</t>
+          <t>356631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396562</t>
+          <t>393618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>767523</t>
+          <t>768835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818259</t>
+          <t>818468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24836</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54848</t>
+          <t>54963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88342</t>
+          <t>87395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>101188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140319</t>
+          <t>139197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164779</t>
+          <t>165717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213775</t>
+          <t>214189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>233892</t>
+          <t>234042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>264018</t>
+          <t>263903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>232658</t>
+          <t>232455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>264688</t>
+          <t>264830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>477945</t>
+          <t>477295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>521705</t>
+          <t>521847</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,76%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,62 +1793,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6502</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7056</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>53518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>70582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102754</t>
+          <t>102957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131588</t>
+          <t>130912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174434</t>
+          <t>175319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>267628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297840</t>
+          <t>297554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>249912</t>
+          <t>249696</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>284198</t>
+          <t>283579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>529243</t>
+          <t>525983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>572826</t>
+          <t>572615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58096</t>
+          <t>59043</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80945</t>
+          <t>83356</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114191</t>
+          <t>116311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149719</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192985</t>
+          <t>195262</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>156551</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178222</t>
+          <t>178489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,82 +2572,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,79%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>165627</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>153362</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>176525</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>85,0%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>334163</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>318265</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>349693</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>77,44%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>165627</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>153403</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>176954</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>79,76%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>334163</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>318039</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>349000</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45059</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,82 +2798,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>22,38%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>41026</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>29982</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>53209</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>74899</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>60230</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>91088</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>22,16%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>41026</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>29780</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>53213</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>25,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>74899</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>59980</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>90332</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>198000</t>
+          <t>197794</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>224834</t>
+          <t>225231</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174082</t>
+          <t>173598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>204356</t>
+          <t>205156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>380339</t>
+          <t>383025</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>423518</t>
+          <t>421149</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,62 +3161,62 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6501</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>44905</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71883</t>
+          <t>71281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72847</t>
+          <t>72047</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103121</t>
+          <t>103605</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>123935</t>
+          <t>126038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>166965</t>
+          <t>164135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>484291</t>
+          <t>482883</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>522919</t>
+          <t>521671</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>445891</t>
+          <t>447118</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>490741</t>
+          <t>490820</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>942977</t>
+          <t>943036</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1001546</t>
+          <t>999246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89251</t>
+          <t>90778</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>127609</t>
+          <t>129378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>141902</t>
+          <t>141901</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186435</t>
+          <t>185569</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>242627</t>
+          <t>245119</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>300431</t>
+          <t>301551</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>624230</t>
+          <t>625230</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>662770</t>
+          <t>665101</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>607711</t>
+          <t>607811</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>654841</t>
+          <t>655241</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,47 +3975,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>83,63%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>1276456</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>1245720</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1303017</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>83,58%</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>1276456</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>1244264</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1300972</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27343</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>77745</t>
+          <t>75543</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>114326</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>116981</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>158131</t>
+          <t>161842</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>207204</t>
+          <t>208609</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>262795</t>
+          <t>263555</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41146</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>503666</t>
+          <t>496109</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>586503</t>
+          <t>585024</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>737331</t>
+          <t>742014</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>835566</t>
+          <t>839809</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1262273</t>
+          <t>1265979</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1389605</t>
+          <t>1392780</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>175052</t>
+          <t>176770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>208424</t>
+          <t>208577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>154694</t>
+          <t>158575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191022</t>
+          <t>191231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>343600</t>
+          <t>342907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>391492</t>
+          <t>390348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78547</t>
+          <t>79205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112604</t>
+          <t>111437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88392</t>
+          <t>89032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123827</t>
+          <t>120642</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>175776</t>
+          <t>178885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>221288</t>
+          <t>227155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354417</t>
+          <t>353298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393973</t>
+          <t>392657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299119</t>
+          <t>299356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347130</t>
+          <t>345571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>668858</t>
+          <t>667505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728875</t>
+          <t>729459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108081</t>
+          <t>108739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147273</t>
+          <t>147602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>170009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>216274</t>
+          <t>216793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290410</t>
+          <t>288409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>351533</t>
+          <t>349402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>232632</t>
+          <t>233081</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>262028</t>
+          <t>261991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>227355</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>261759</t>
+          <t>261906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>469046</t>
+          <t>470122</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>516114</t>
+          <t>514683</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86773</t>
+          <t>87322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74888</t>
+          <t>75273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108875</t>
+          <t>110976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140842</t>
+          <t>142556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186840</t>
+          <t>187029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>275398</t>
+          <t>275224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>309845</t>
+          <t>307695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263100</t>
+          <t>263379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>299798</t>
+          <t>300125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>553429</t>
+          <t>551891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>601238</t>
+          <t>602940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60002</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93565</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>84070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119689</t>
+          <t>119384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>152492</t>
+          <t>150947</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>199332</t>
+          <t>201792</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164109</t>
+          <t>163635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185940</t>
+          <t>185444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124604</t>
+          <t>126182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153649</t>
+          <t>155533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296861</t>
+          <t>296601</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>334762</t>
+          <t>333847</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61150</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90686</t>
+          <t>88340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92546</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129573</t>
+          <t>128911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194821</t>
+          <t>195904</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>222544</t>
+          <t>223855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>168846</t>
+          <t>167685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200226</t>
+          <t>198582</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>369696</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>414061</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77143</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76577</t>
+          <t>76744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107498</t>
+          <t>107938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134529</t>
+          <t>132947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>176202</t>
+          <t>177508</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>493275</t>
+          <t>494383</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>536483</t>
+          <t>539346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>479990</t>
+          <t>480189</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>530602</t>
+          <t>528081</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>987250</t>
+          <t>993058</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1053176</t>
+          <t>1054739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14901</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23739</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>33218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>117508</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>161576</t>
+          <t>159949</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>151340</t>
+          <t>153306</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199379</t>
+          <t>200127</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>282181</t>
+          <t>280949</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>345042</t>
+          <t>341235</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>688021</t>
+          <t>688913</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>723572</t>
+          <t>723975</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>694662</t>
+          <t>696783</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>736201</t>
+          <t>736921</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1396239</t>
+          <t>1395693</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1448302</t>
+          <t>1448367</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>21099</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>50682</t>
+          <t>50424</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>86043</t>
+          <t>85830</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>78403</t>
+          <t>79878</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>118009</t>
+          <t>117690</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>139479</t>
+          <t>140261</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>191353</t>
+          <t>191669</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2664835</t>
+          <t>2665805</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2765436</t>
+          <t>2763114</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2517014</t>
+          <t>2512312</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2627981</t>
+          <t>2626234</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5216196</t>
+          <t>5214702</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5363595</t>
+          <t>5365185</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>48047</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>70044</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>71010</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>110159</t>
+          <t>108278</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624815</t>
+          <t>625178</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>722862</t>
+          <t>719993</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>875423</t>
+          <t>876962</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986990</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1530467</t>
+          <t>1520447</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1673651</t>
+          <t>1673178</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>192061</t>
+          <t>194903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225701</t>
+          <t>225860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>165483</t>
+          <t>164468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196387</t>
+          <t>197536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>369055</t>
+          <t>370117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>415979</t>
+          <t>415743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>63782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95405</t>
+          <t>93789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89198</t>
+          <t>88163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120692</t>
+          <t>120731</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158202</t>
+          <t>159199</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205452</t>
+          <t>204787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401171</t>
+          <t>402389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434646</t>
+          <t>435921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391273</t>
+          <t>392922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>431926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808265</t>
+          <t>803133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859621</t>
+          <t>855567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65887</t>
+          <t>63723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>96818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88662</t>
+          <t>86658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126045</t>
+          <t>124618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158166</t>
+          <t>161078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209578</t>
+          <t>213956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264099</t>
+          <t>264144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285682</t>
+          <t>285936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>272615</t>
+          <t>271587</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>298096</t>
+          <t>298323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>544140</t>
+          <t>543368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>577534</t>
+          <t>578625</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38275</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>28693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53278</t>
+          <t>53044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85028</t>
+          <t>85818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251938</t>
+          <t>252314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>285589</t>
+          <t>287377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>242756</t>
+          <t>241847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>281238</t>
+          <t>282196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>505162</t>
+          <t>500799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>558898</t>
+          <t>557437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79193</t>
+          <t>76792</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113047</t>
+          <t>111711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99394</t>
+          <t>97154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>138767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>187446</t>
+          <t>189013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>238695</t>
+          <t>242335</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170791</t>
+          <t>173038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190497</t>
+          <t>191811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177264</t>
+          <t>175357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>196826</t>
+          <t>196009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>355175</t>
+          <t>354550</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>382222</t>
+          <t>382837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35413</t>
+          <t>36681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>38154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>63400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>190455</t>
+          <t>191362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>217186</t>
+          <t>219025</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>181247</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210647</t>
+          <t>210893</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>381852</t>
+          <t>381402</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>422294</t>
+          <t>421867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38226</t>
+          <t>36534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62601</t>
+          <t>61365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60770</t>
+          <t>59706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89112</t>
+          <t>89259</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105519</t>
+          <t>104942</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144497</t>
+          <t>143350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>563554</t>
+          <t>560657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>597757</t>
+          <t>597608</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>542870</t>
+          <t>543151</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>585134</t>
+          <t>586131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1118794</t>
+          <t>1118785</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1172526</t>
+          <t>1172030</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34313</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>43621</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51820</t>
+          <t>53323</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85512</t>
+          <t>87229</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82365</t>
+          <t>85751</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122912</t>
+          <t>123844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>146085</t>
+          <t>145349</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>195469</t>
+          <t>196484</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>653360</t>
+          <t>655053</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>691638</t>
+          <t>693623</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>660511</t>
+          <t>660197</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>703959</t>
+          <t>704662</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1329337</t>
+          <t>1327379</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1388337</t>
+          <t>1386189</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>79193</t>
+          <t>77409</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116996</t>
+          <t>114643</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>112784</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>155198</t>
+          <t>155602</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>201626</t>
+          <t>201343</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>256852</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2775333</t>
+          <t>2778181</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2865037</t>
+          <t>2862451</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2728136</t>
+          <t>2720750</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2828072</t>
+          <t>2823808</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5528400</t>
+          <t>5529828</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5663983</t>
+          <t>5664986</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78036</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,47 +13224,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>106763</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>87875</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>132022</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>106763</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>87126</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>130455</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>474563</t>
+          <t>479418</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>559970</t>
+          <t>559088</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>652560</t>
+          <t>655834</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>747184</t>
+          <t>758355</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1152672</t>
+          <t>1156904</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1285740</t>
+          <t>1286180</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182746</t>
+          <t>182281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223737</t>
+          <t>224426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161651</t>
+          <t>161768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190321</t>
+          <t>189038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>355379</t>
+          <t>355463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406721</t>
+          <t>405745</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86262</t>
+          <t>85916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127512</t>
+          <t>127519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96872</t>
+          <t>98206</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125482</t>
+          <t>125456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>191572</t>
+          <t>191620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>241823</t>
+          <t>241477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413170</t>
+          <t>416048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457123</t>
+          <t>457635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393597</t>
+          <t>394073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425499</t>
+          <t>424945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823376</t>
+          <t>824243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876690</t>
+          <t>878277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>515</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61267</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105220</t>
+          <t>102342</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85987</t>
+          <t>87262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117834</t>
+          <t>118012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153708</t>
+          <t>151995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207973</t>
+          <t>206447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>228741</t>
+          <t>228008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257848</t>
+          <t>257734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219717</t>
+          <t>220404</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250214</t>
+          <t>250722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>459599</t>
+          <t>460163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>499828</t>
+          <t>502854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55831</t>
+          <t>55970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84529</t>
+          <t>85824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93724</t>
+          <t>93751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123869</t>
+          <t>123350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158744</t>
+          <t>155691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198423</t>
+          <t>197337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214233</t>
+          <t>215251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>251712</t>
+          <t>252006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>355525</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>420001</t>
+          <t>420076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>581371</t>
+          <t>584773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>664380</t>
+          <t>667139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57755</t>
+          <t>57227</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95977</t>
+          <t>93959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54195</t>
+          <t>53736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115195</t>
+          <t>115669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118542</t>
+          <t>115837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>200659</t>
+          <t>196268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153381</t>
+          <t>151199</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167859</t>
+          <t>167713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193877</t>
+          <t>193780</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201971</t>
+          <t>202037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>350825</t>
+          <t>350672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367370</t>
+          <t>367378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -15690,97 +15690,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36573</t>
+          <t>36726</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187704</t>
+          <t>187740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213384</t>
+          <t>212606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169389</t>
+          <t>169119</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193130</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>363670</t>
+          <t>365586</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>399431</t>
+          <t>399345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>55275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80907</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>63939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87358</t>
+          <t>87375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>124762</t>
+          <t>125768</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>158921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>427883</t>
+          <t>427850</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>483793</t>
+          <t>480314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>170307</t>
+          <t>204712</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>557980</t>
+          <t>559710</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>542632</t>
+          <t>499804</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1028503</t>
+          <t>1026981</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21125</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132448</t>
+          <t>135034</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>187577</t>
+          <t>186098</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>270687</t>
+          <t>270157</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>666372</t>
+          <t>633068</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>417930</t>
+          <t>418262</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>913020</t>
+          <t>952518</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>799082</t>
+          <t>797311</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>894204</t>
+          <t>890796</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>585862</t>
+          <t>586518</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>619469</t>
+          <t>619549</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1396229</t>
+          <t>1396591</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1521915</t>
+          <t>1518309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>125391</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>92088</t>
+          <t>92123</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>126110</t>
+          <t>124652</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>124758</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>240140</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2708867</t>
+          <t>2702110</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2931030</t>
+          <t>2933540</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2074693</t>
+          <t>2118192</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2781717</t>
+          <t>2779790</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4822798</t>
+          <t>4788190</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5607577</t>
+          <t>5585163</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>61259</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>512316</t>
+          <t>509372</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>729500</t>
+          <t>735800</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>843702</t>
+          <t>843271</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1555264</t>
+          <t>1507931</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1459473</t>
+          <t>1479337</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2251053</t>
+          <t>2298887</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
